--- a/data/trans_dic/P36BPD07_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD07_R-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,88; 91,8</t>
+          <t>86,88; 91,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,37; 78,22</t>
+          <t>71,28; 78,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,19; 92,05</t>
+          <t>87,42; 91,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,87; 83,07</t>
+          <t>77,11; 82,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,73; 91,31</t>
+          <t>87,79; 91,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,52; 79,93</t>
+          <t>75,29; 79,62</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,15; 85,14</t>
+          <t>80,24; 85,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,14; 87,84</t>
+          <t>63,77; 70,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,45; 88,57</t>
+          <t>84,43; 88,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,12; 75,2</t>
+          <t>69,48; 74,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,19; 86,46</t>
+          <t>83,22; 86,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,44; 81,89</t>
+          <t>67,59; 71,76</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,29; 85,27</t>
+          <t>79,33; 85,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,09; 79,49</t>
+          <t>71,92; 79,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,71; 85,26</t>
+          <t>79,87; 85,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,79; 92,24</t>
+          <t>75,99; 81,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,35; 84,45</t>
+          <t>80,72; 84,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,18; 87,11</t>
+          <t>75,08; 79,51</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,42; 86,21</t>
+          <t>81,22; 86,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,31; 75,14</t>
+          <t>66,65; 73,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,64; 89,85</t>
+          <t>85,59; 89,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,96; 82,7</t>
+          <t>73,54; 78,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,32; 87,51</t>
+          <t>84,23; 87,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,27; 78,31</t>
+          <t>71,25; 75,35</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,09; 85,7</t>
+          <t>83,16; 85,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,27; 79,78</t>
+          <t>69,74; 73,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,58; 87,81</t>
+          <t>85,58; 87,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,94; 82,6</t>
+          <t>74,95; 77,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,78; 86,46</t>
+          <t>84,7; 86,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,64; 79,51</t>
+          <t>72,88; 75,07</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>472553</t>
+          <t>516047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>544348</t>
+          <t>586541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1016900</t>
+          <t>1102588</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>583319; 616338</t>
+          <t>583341; 616207</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>445774; 495513</t>
+          <t>490833; 539863</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>582703; 615194</t>
+          <t>584273; 614839</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>525440; 560538</t>
+          <t>564505; 604964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1175391; 1223269</t>
+          <t>1176219; 1222491</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>988068; 1045716</t>
+          <t>1069538; 1131038</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>882197</t>
+          <t>704343</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>696886</t>
+          <t>770271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1579082</t>
+          <t>1474615</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>816703; 867486</t>
+          <t>817574; 867205</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>788390; 1047127</t>
+          <t>668371; 742387</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>880735; 923694</t>
+          <t>880519; 924610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>671552; 720214</t>
+          <t>742960; 796466</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1715199; 1782595</t>
+          <t>1715853; 1778401</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1492754; 1760550</t>
+          <t>1431050; 1519346</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>534829</t>
+          <t>609852</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>786721</t>
+          <t>639227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1321550</t>
+          <t>1249079</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>599461; 644694</t>
+          <t>599825; 643930</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>508016; 560181</t>
+          <t>577592; 638371</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>619639; 662761</t>
+          <t>620882; 664568</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>735388; 860902</t>
+          <t>617252; 660922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1232140; 1294993</t>
+          <t>1237738; 1297499</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1264256; 1426882</t>
+          <t>1212799; 1284366</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>662598</t>
+          <t>690762</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>858346</t>
+          <t>848381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1520945</t>
+          <t>1539142</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>752902; 797201</t>
+          <t>751034; 795796</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>631700; 694905</t>
+          <t>658466; 721830</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885235; 928737</t>
+          <t>884746; 926495</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>828277; 901696</t>
+          <t>819475; 873137</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1651357; 1713757</t>
+          <t>1649530; 1715303</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1476416; 1578119</t>
+          <t>1497931; 1583955</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2800989; 2889160</t>
+          <t>2803345; 2886551</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2462346; 2756369</t>
+          <t>2460119; 2583832</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3014471; 3093012</t>
+          <t>3014342; 3093238</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2813060; 3020270</t>
+          <t>2794219; 2894783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5843895; 5960210</t>
+          <t>5838447; 5961622</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5307759; 5654380</t>
+          <t>5287905; 5446729</t>
         </is>
       </c>
     </row>
